--- a/dist/catalog.xlsx
+++ b/dist/catalog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/astrid/FilesLocal/Projects/mara-voss-portfolio/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/astrid/GitHub/personal-portfolio/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72530F2D-465A-4649-9863-2A52A9E1C1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9415CD1-9542-D346-9AEF-D71DC85F45DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="18480" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="63">
   <si>
     <t>file</t>
   </si>
@@ -124,141 +124,6 @@
     <t>48 × 60 in</t>
   </si>
   <si>
-    <t>DSC_3793.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3800.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3803.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3804.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3807.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3809.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3810.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3812.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3814.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3816.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3818.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3821.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3822.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3824.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3826.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3828.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3831.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3835.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3837.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3838.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3841.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3843.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3845.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3848.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3851.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3855.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3857.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3860.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3861.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3863.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3866.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3868.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3870.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3872.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3874.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3878.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3880.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3881.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3884.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3885.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3888.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3889.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3894.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3896.JPG</t>
-  </si>
-  <si>
-    <t>DSC_3898.JPG</t>
-  </si>
-  <si>
     <t>49 × 60 in</t>
   </si>
   <si>
@@ -289,82 +154,61 @@
     <t>58 × 60 in</t>
   </si>
   <si>
-    <t>59 × 60 in</t>
-  </si>
-  <si>
-    <t>60 × 60 in</t>
-  </si>
-  <si>
-    <t>61 × 60 in</t>
-  </si>
-  <si>
-    <t>62 × 60 in</t>
-  </si>
-  <si>
-    <t>63 × 60 in</t>
-  </si>
-  <si>
-    <t>64 × 60 in</t>
-  </si>
-  <si>
-    <t>65 × 60 in</t>
-  </si>
-  <si>
-    <t>66 × 60 in</t>
-  </si>
-  <si>
-    <t>67 × 60 in</t>
-  </si>
-  <si>
-    <t>68 × 60 in</t>
-  </si>
-  <si>
-    <t>69 × 60 in</t>
-  </si>
-  <si>
-    <t>70 × 60 in</t>
-  </si>
-  <si>
-    <t>71 × 60 in</t>
-  </si>
-  <si>
-    <t>72 × 60 in</t>
-  </si>
-  <si>
-    <t>73 × 60 in</t>
-  </si>
-  <si>
-    <t>74 × 60 in</t>
-  </si>
-  <si>
-    <t>75 × 60 in</t>
-  </si>
-  <si>
-    <t>76 × 60 in</t>
-  </si>
-  <si>
-    <t>77 × 60 in</t>
-  </si>
-  <si>
-    <t>78 × 60 in</t>
-  </si>
-  <si>
-    <t>79 × 60 in</t>
-  </si>
-  <si>
-    <t>80 × 60 in</t>
-  </si>
-  <si>
-    <t>81 × 60 in</t>
-  </si>
-  <si>
-    <t>82 × 60 in</t>
-  </si>
-  <si>
-    <t>83 × 60 in</t>
-  </si>
-  <si>
-    <t>84 × 60 in</t>
+    <t>thumb-exhibit-01.jpg</t>
+  </si>
+  <si>
+    <t>thumb-exhibit-02.jpg</t>
+  </si>
+  <si>
+    <t>thumb-exhibit-03.jpg</t>
+  </si>
+  <si>
+    <t>thumb-exhibit-04.jpg</t>
+  </si>
+  <si>
+    <t>thumb-exhibit-05.jpg</t>
+  </si>
+  <si>
+    <t>thumb-exhibit-06.jpg</t>
+  </si>
+  <si>
+    <t>thumb-exhibit-07.jpg</t>
+  </si>
+  <si>
+    <t>thumb-exhibit-08.jpg</t>
+  </si>
+  <si>
+    <t>thumb-exhibit-09.jpg</t>
+  </si>
+  <si>
+    <t>tooplate-about-image.jpg</t>
+  </si>
+  <si>
+    <t>tooplate-exhibit-01.jpg</t>
+  </si>
+  <si>
+    <t>tooplate-exhibit-02.jpg</t>
+  </si>
+  <si>
+    <t>tooplate-exhibit-03.jpg</t>
+  </si>
+  <si>
+    <t>tooplate-exhibit-04.jpg</t>
+  </si>
+  <si>
+    <t>tooplate-exhibit-05.jpg</t>
+  </si>
+  <si>
+    <t>tooplate-exhibit-06.jpg</t>
+  </si>
+  <si>
+    <t>tooplate-exhibit-07.jpg</t>
+  </si>
+  <si>
+    <t>tooplate-exhibit-08.jpg</t>
+  </si>
+  <si>
+    <t>tooplate-exhibit-09.jpg</t>
   </si>
 </sst>
 </file>
@@ -747,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
@@ -783,7 +627,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -803,7 +647,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -823,7 +667,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -843,7 +687,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
@@ -863,7 +707,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
@@ -883,7 +727,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -903,7 +747,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
@@ -923,7 +767,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
@@ -943,7 +787,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
@@ -963,7 +807,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -978,12 +822,12 @@
         <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -998,12 +842,12 @@
         <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>80</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
@@ -1018,12 +862,12 @@
         <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
@@ -1038,12 +882,12 @@
         <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -1058,12 +902,12 @@
         <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -1078,12 +922,12 @@
         <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
@@ -1098,12 +942,12 @@
         <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -1118,12 +962,12 @@
         <v>32</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -1138,12 +982,12 @@
         <v>32</v>
       </c>
       <c r="F19" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -1158,527 +1002,7 @@
         <v>32</v>
       </c>
       <c r="F20" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21">
-        <v>2023</v>
-      </c>
-      <c r="D21">
-        <v>7</v>
-      </c>
-      <c r="E21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22">
-        <v>2023</v>
-      </c>
-      <c r="D22">
-        <v>7</v>
-      </c>
-      <c r="E22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23">
-        <v>2023</v>
-      </c>
-      <c r="D23">
-        <v>7</v>
-      </c>
-      <c r="E23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24">
-        <v>2023</v>
-      </c>
-      <c r="D24">
-        <v>7</v>
-      </c>
-      <c r="E24" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25">
-        <v>2023</v>
-      </c>
-      <c r="D25">
-        <v>7</v>
-      </c>
-      <c r="E25" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26">
-        <v>2023</v>
-      </c>
-      <c r="D26">
-        <v>7</v>
-      </c>
-      <c r="E26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27">
-        <v>2023</v>
-      </c>
-      <c r="D27">
-        <v>7</v>
-      </c>
-      <c r="E27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28">
-        <v>2023</v>
-      </c>
-      <c r="D28">
-        <v>7</v>
-      </c>
-      <c r="E28" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29">
-        <v>2023</v>
-      </c>
-      <c r="D29">
-        <v>7</v>
-      </c>
-      <c r="E29" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30">
-        <v>2023</v>
-      </c>
-      <c r="D30">
-        <v>7</v>
-      </c>
-      <c r="E30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31">
-        <v>2023</v>
-      </c>
-      <c r="D31">
-        <v>7</v>
-      </c>
-      <c r="E31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32">
-        <v>2023</v>
-      </c>
-      <c r="D32">
-        <v>7</v>
-      </c>
-      <c r="E32" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33">
-        <v>2023</v>
-      </c>
-      <c r="D33">
-        <v>7</v>
-      </c>
-      <c r="E33" t="s">
-        <v>32</v>
-      </c>
-      <c r="F33" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34">
-        <v>2023</v>
-      </c>
-      <c r="D34">
-        <v>7</v>
-      </c>
-      <c r="E34" t="s">
-        <v>32</v>
-      </c>
-      <c r="F34" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>67</v>
-      </c>
-      <c r="B35" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35">
-        <v>2023</v>
-      </c>
-      <c r="D35">
-        <v>7</v>
-      </c>
-      <c r="E35" t="s">
-        <v>32</v>
-      </c>
-      <c r="F35" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>68</v>
-      </c>
-      <c r="B36" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36">
-        <v>2023</v>
-      </c>
-      <c r="D36">
-        <v>7</v>
-      </c>
-      <c r="E36" t="s">
-        <v>32</v>
-      </c>
-      <c r="F36" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>69</v>
-      </c>
-      <c r="B37" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37">
-        <v>2023</v>
-      </c>
-      <c r="D37">
-        <v>7</v>
-      </c>
-      <c r="E37" t="s">
-        <v>32</v>
-      </c>
-      <c r="F37" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>70</v>
-      </c>
-      <c r="B38" t="s">
-        <v>31</v>
-      </c>
-      <c r="C38">
-        <v>2023</v>
-      </c>
-      <c r="D38">
-        <v>7</v>
-      </c>
-      <c r="E38" t="s">
-        <v>32</v>
-      </c>
-      <c r="F38" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>71</v>
-      </c>
-      <c r="B39" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39">
-        <v>2023</v>
-      </c>
-      <c r="D39">
-        <v>7</v>
-      </c>
-      <c r="E39" t="s">
-        <v>32</v>
-      </c>
-      <c r="F39" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>72</v>
-      </c>
-      <c r="B40" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40">
-        <v>2023</v>
-      </c>
-      <c r="D40">
-        <v>7</v>
-      </c>
-      <c r="E40" t="s">
-        <v>32</v>
-      </c>
-      <c r="F40" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>73</v>
-      </c>
-      <c r="B41" t="s">
-        <v>31</v>
-      </c>
-      <c r="C41">
-        <v>2023</v>
-      </c>
-      <c r="D41">
-        <v>7</v>
-      </c>
-      <c r="E41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>74</v>
-      </c>
-      <c r="B42" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42">
-        <v>2023</v>
-      </c>
-      <c r="D42">
-        <v>7</v>
-      </c>
-      <c r="E42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F42" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>75</v>
-      </c>
-      <c r="B43" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43">
-        <v>2023</v>
-      </c>
-      <c r="D43">
-        <v>7</v>
-      </c>
-      <c r="E43" t="s">
-        <v>32</v>
-      </c>
-      <c r="F43" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>76</v>
-      </c>
-      <c r="B44" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44">
-        <v>2023</v>
-      </c>
-      <c r="D44">
-        <v>7</v>
-      </c>
-      <c r="E44" t="s">
-        <v>32</v>
-      </c>
-      <c r="F44" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>77</v>
-      </c>
-      <c r="B45" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45">
-        <v>2023</v>
-      </c>
-      <c r="D45">
-        <v>7</v>
-      </c>
-      <c r="E45" t="s">
-        <v>32</v>
-      </c>
-      <c r="F45" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>78</v>
-      </c>
-      <c r="B46" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46">
-        <v>2026</v>
-      </c>
-      <c r="D46">
-        <v>7</v>
-      </c>
-      <c r="E46" t="s">
-        <v>32</v>
-      </c>
-      <c r="F46" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/dist/catalog.xlsx
+++ b/dist/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/astrid/GitHub/personal-portfolio/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9415CD1-9542-D346-9AEF-D71DC85F45DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB63AAEB-F5E8-B049-8093-B5B327714203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="18480" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="69">
   <si>
     <t>file</t>
   </si>
@@ -209,6 +209,24 @@
   </si>
   <si>
     <t>tooplate-exhibit-09.jpg</t>
+  </si>
+  <si>
+    <t>collections</t>
+  </si>
+  <si>
+    <t>[Spring]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Fall], [Landscape] </t>
+  </si>
+  <si>
+    <t>[Landscape], [Spring]</t>
+  </si>
+  <si>
+    <t>[Landscape]</t>
+  </si>
+  <si>
+    <t>[other]</t>
   </si>
 </sst>
 </file>
@@ -591,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
@@ -602,7 +620,7 @@
     <col min="7" max="7" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -624,8 +642,11 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -644,8 +665,11 @@
       <c r="F2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -665,7 +689,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -684,8 +708,11 @@
       <c r="F4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -705,7 +732,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>48</v>
       </c>
@@ -725,7 +752,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -745,7 +772,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>50</v>
       </c>
@@ -765,7 +792,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -785,7 +812,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -805,7 +832,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -824,8 +851,11 @@
       <c r="F11" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -845,7 +875,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -865,7 +895,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -884,8 +914,11 @@
       <c r="F14" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -905,7 +938,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>58</v>
       </c>
@@ -925,7 +958,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -944,8 +977,11 @@
       <c r="F17" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -964,8 +1000,11 @@
       <c r="F18" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -985,7 +1024,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>62</v>
       </c>

--- a/dist/catalog.xlsx
+++ b/dist/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/astrid/GitHub/personal-portfolio/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB63AAEB-F5E8-B049-8093-B5B327714203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AE6331-2BB2-A349-8490-A7E52CD72B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="18480" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="73">
   <si>
     <t>file</t>
   </si>
@@ -227,6 +227,18 @@
   </si>
   <si>
     <t>[other]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[this], [there], [apple], [banana], </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[other], [together], [paint], [sketch], [gesso], </t>
+  </si>
+  <si>
+    <t>[more], [less]</t>
+  </si>
+  <si>
+    <t>[more]</t>
   </si>
 </sst>
 </file>
@@ -751,6 +763,9 @@
       <c r="F6" t="s">
         <v>21</v>
       </c>
+      <c r="H6" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -771,6 +786,9 @@
       <c r="F7" t="s">
         <v>24</v>
       </c>
+      <c r="H7" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -791,6 +809,9 @@
       <c r="F8" t="s">
         <v>27</v>
       </c>
+      <c r="H8" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -1023,6 +1044,9 @@
       <c r="F19" t="s">
         <v>42</v>
       </c>
+      <c r="H19" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
@@ -1042,6 +1066,9 @@
       </c>
       <c r="F20" t="s">
         <v>43</v>
+      </c>
+      <c r="H20" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/dist/catalog.xlsx
+++ b/dist/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/astrid/GitHub/personal-portfolio/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AE6331-2BB2-A349-8490-A7E52CD72B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F41C65-1687-EE47-85C3-3F371E3C85E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="18480" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="72">
   <si>
     <t>file</t>
   </si>
@@ -224,9 +224,6 @@
   </si>
   <si>
     <t>[Landscape]</t>
-  </si>
-  <si>
-    <t>[other]</t>
   </si>
   <si>
     <t xml:space="preserve">[this], [there], [apple], [banana], </t>
@@ -764,7 +761,7 @@
         <v>21</v>
       </c>
       <c r="H6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -787,7 +784,7 @@
         <v>24</v>
       </c>
       <c r="H7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -810,7 +807,7 @@
         <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -852,6 +849,9 @@
       <c r="F10" t="s">
         <v>33</v>
       </c>
+      <c r="H10" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -895,6 +895,9 @@
       <c r="F12" t="s">
         <v>35</v>
       </c>
+      <c r="H12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -915,6 +918,9 @@
       <c r="F13" t="s">
         <v>36</v>
       </c>
+      <c r="H13" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -958,6 +964,9 @@
       <c r="F15" t="s">
         <v>38</v>
       </c>
+      <c r="H15" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -978,6 +987,9 @@
       <c r="F16" t="s">
         <v>39</v>
       </c>
+      <c r="H16" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -1022,7 +1034,7 @@
         <v>41</v>
       </c>
       <c r="H18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -1045,7 +1057,7 @@
         <v>42</v>
       </c>
       <c r="H19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -1068,7 +1080,7 @@
         <v>43</v>
       </c>
       <c r="H20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/dist/catalog.xlsx
+++ b/dist/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/astrid/GitHub/personal-portfolio/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F41C65-1687-EE47-85C3-3F371E3C85E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DB741B-2535-B04D-BBA0-0651F103E144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="18480" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="78">
   <si>
     <t>file</t>
   </si>
@@ -236,6 +236,24 @@
   </si>
   <si>
     <t>[more]</t>
+  </si>
+  <si>
+    <t>canvas-a.jpg</t>
+  </si>
+  <si>
+    <t>canvas-b.jpg</t>
+  </si>
+  <si>
+    <t>59 × 60 in</t>
+  </si>
+  <si>
+    <t>60 × 60 in</t>
+  </si>
+  <si>
+    <t>layout</t>
+  </si>
+  <si>
+    <t>offset</t>
   </si>
 </sst>
 </file>
@@ -618,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
@@ -627,9 +645,10 @@
     <col min="5" max="5" width="28.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="24.83203125" customWidth="1"/>
+    <col min="8" max="8" width="38.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -654,8 +673,11 @@
       <c r="H1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -678,7 +700,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -698,7 +720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -721,7 +743,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -741,7 +763,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>48</v>
       </c>
@@ -764,7 +786,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -787,7 +809,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>50</v>
       </c>
@@ -810,7 +832,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -830,7 +852,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>52</v>
       </c>
@@ -853,7 +875,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -876,7 +898,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -899,7 +921,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -922,7 +944,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -945,7 +967,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -968,7 +990,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>58</v>
       </c>
@@ -991,7 +1013,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -1014,7 +1036,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -1037,7 +1059,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -1060,7 +1082,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>62</v>
       </c>
@@ -1081,6 +1103,58 @@
       </c>
       <c r="H20" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21">
+        <v>2026</v>
+      </c>
+      <c r="D21">
+        <v>7</v>
+      </c>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
+        <v>74</v>
+      </c>
+      <c r="H21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22">
+        <v>2026</v>
+      </c>
+      <c r="D22">
+        <v>7</v>
+      </c>
+      <c r="E22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
